--- a/BaoCaoTracking/BaoCao_Tracking_28-04-2026.xlsx
+++ b/BaoCaoTracking/BaoCao_Tracking_28-04-2026.xlsx
@@ -155,6 +155,21 @@
   </x:si>
   <x:si>
     <x:t>lưu file excel design mới</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ca 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nguyễn Phi Học</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00026796354</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M02-01-C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>uyển test</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -809,14 +824,14 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J12"/>
+  <x:dimension ref="A1:J13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="16.710625" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="7.424911" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="32.996339" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="19.282054" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="20.996339" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="24.710625" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="19.424911" style="1" customWidth="1"/>
     <x:col min="7" max="7" width="27.139196" style="1" customWidth="1"/>
@@ -1103,35 +1118,67 @@
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
-      <x:c r="A12" s="13" t="s">
+      <x:c r="A12" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B12" s="14" t="s">
+      <x:c r="B12" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="C12" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D12" s="14" t="s">
+      <x:c r="D12" s="11" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="E12" s="11" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="F12" s="11" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G12" s="14">
+      <x:c r="G12" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H12" s="14" t="s">
+      <x:c r="H12" s="11" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I12" s="14">
+      <x:c r="I12" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="s">
+      <x:c r="J12" s="12" t="s">
         <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:10">
+      <x:c r="A13" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G13" s="14">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I13" s="14">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/BaoCaoTracking/BaoCao_Tracking_28-04-2026.xlsx
+++ b/BaoCaoTracking/BaoCao_Tracking_28-04-2026.xlsx
@@ -170,6 +170,48 @@
   </x:si>
   <x:si>
     <x:t>uyển test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00002673</x:t>
+  </x:si>
+  <x:si>
+    <x:t>021*5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M05-03-D</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M03-03-A, M05-02-D</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test search sku *</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0001696219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1796*3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M02-04-A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sku</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0002691456</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sku lưu *</x:t>
+  </x:si>
+  <x:si>
+    <x:t>000000000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M05-04-B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>**</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -824,7 +866,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J13"/>
+  <x:dimension ref="A1:J17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1150,35 +1192,163 @@
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
-      <x:c r="A13" s="13" t="s">
+      <x:c r="A13" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B13" s="14" t="s">
+      <x:c r="B13" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="C13" s="11" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D13" s="14" t="s">
+      <x:c r="D13" s="11" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="E13" s="11" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="F13" s="11" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G13" s="14">
+      <x:c r="G13" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H13" s="14" t="s">
+      <x:c r="H13" s="11" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="I13" s="14">
+      <x:c r="I13" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="s">
+      <x:c r="J13" s="12" t="s">
         <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:10">
+      <x:c r="A14" s="10" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G14" s="11">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I14" s="11">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:10">
+      <x:c r="A15" s="10" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G15" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I15" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:10">
+      <x:c r="A16" s="10" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G16" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I16" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10">
+      <x:c r="A17" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G17" s="14">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I17" s="14">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
+        <x:v>65</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/BaoCaoTracking/BaoCao_Tracking_28-04-2026.xlsx
+++ b/BaoCaoTracking/BaoCao_Tracking_28-04-2026.xlsx
@@ -55,9 +55,15 @@
     <x:t>NOTE</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-27 23:00:41</x:t>
+  </x:si>
+  <x:si>
     <x:t/>
   </x:si>
   <x:si>
+    <x:t>2026-04-27 16:13:47</x:t>
+  </x:si>
+  <x:si>
     <x:t>27/4/2026</x:t>
   </x:si>
   <x:si>
@@ -82,6 +88,9 @@
     <x:t>test lưu vào db</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-27 17:02:30</x:t>
+  </x:si>
+  <x:si>
     <x:t>28/4/2026</x:t>
   </x:si>
   <x:si>
@@ -100,6 +109,9 @@
     <x:t>test lưu đồng bộ</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-28 00:17:48</x:t>
+  </x:si>
+  <x:si>
     <x:t>07538520</x:t>
   </x:si>
   <x:si>
@@ -115,6 +127,9 @@
     <x:t>DONE</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-28 00:23:35</x:t>
+  </x:si>
+  <x:si>
     <x:t>95100</x:t>
   </x:si>
   <x:si>
@@ -130,6 +145,9 @@
     <x:t>test fix time, save excel</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-28 00:27:46</x:t>
+  </x:si>
+  <x:si>
     <x:t>0000267456</x:t>
   </x:si>
   <x:si>
@@ -145,18 +163,27 @@
     <x:t>hehehhehee</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-28 00:34:41</x:t>
+  </x:si>
+  <x:si>
     <x:t>0000267985</x:t>
   </x:si>
   <x:si>
     <x:t>M02-03-A, M02-08-A</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-28 00:36:45</x:t>
+  </x:si>
+  <x:si>
     <x:t>M02-04-A, M02-01-C</x:t>
   </x:si>
   <x:si>
     <x:t>lưu file excel design mới</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-28 00:50:19</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ca 1</x:t>
   </x:si>
   <x:si>
@@ -172,6 +199,9 @@
     <x:t>uyển test</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-28 14:58:42</x:t>
+  </x:si>
+  <x:si>
     <x:t>00002673</x:t>
   </x:si>
   <x:si>
@@ -187,6 +217,9 @@
     <x:t>test search sku *</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-28 15:05:20</x:t>
+  </x:si>
+  <x:si>
     <x:t>0001696219</x:t>
   </x:si>
   <x:si>
@@ -199,12 +232,18 @@
     <x:t>test sku</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-28 15:09:11</x:t>
+  </x:si>
+  <x:si>
     <x:t>0002691456</x:t>
   </x:si>
   <x:si>
     <x:t>sku lưu *</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-04-28 15:10:25</x:t>
+  </x:si>
+  <x:si>
     <x:t>000000000</x:t>
   </x:si>
   <x:si>
@@ -212,14 +251,57 @@
   </x:si>
   <x:si>
     <x:t>**</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-28 15:47:12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00267985</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6477000000006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M05-15-D</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-28 15:48:48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>000267453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M05-05-C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test quét listid súng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-28 15:56:33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>000267964</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6497000000017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M05-05-B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M05-06-A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>update file excel</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="0" formatCode=""/>
+    <x:numFmt numFmtId="164" formatCode="dd/MM/yyyy HH:mm:ss"/>
   </x:numFmts>
   <x:fonts count="5">
     <x:font>
@@ -487,7 +569,7 @@
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -496,7 +578,7 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -547,7 +629,7 @@
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -559,7 +641,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -866,19 +948,19 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J17"/>
+  <x:dimension ref="A1:J20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
-    <x:col min="1" max="1" width="16.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="7.424911" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="31.139196" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="16.710625" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="32.996339" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="20.996339" style="1" customWidth="1"/>
-    <x:col min="5" max="5" width="24.710625" style="1" customWidth="1"/>
-    <x:col min="6" max="6" width="19.424911" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="25.282054" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="20.996339" style="1" customWidth="1"/>
+    <x:col min="6" max="6" width="24.710625" style="1" customWidth="1"/>
     <x:col min="7" max="7" width="27.139196" style="1" customWidth="1"/>
-    <x:col min="8" max="8" width="32.424911" style="1" customWidth="1"/>
-    <x:col min="9" max="9" width="28.424911" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="20.710625" style="1" customWidth="1"/>
+    <x:col min="9" max="9" width="32.424911" style="1" customWidth="1"/>
     <x:col min="10" max="10" width="37.139196" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -940,415 +1022,511 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G5" s="11">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H5" s="11">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H5" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I5" s="11">
-        <x:v>0</x:v>
+      <x:c r="I5" s="11" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J5" s="12" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="10" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G6" s="11">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H6" s="11">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I6" s="11">
-        <x:v>5</x:v>
+      <x:c r="I6" s="11" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J6" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E7" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F7" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G7" s="11">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H7" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I7" s="11">
-        <x:v>2</x:v>
+      <x:c r="I7" s="11" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J7" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B8" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D8" s="11" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E8" s="11" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F8" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G8" s="11">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H8" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H8" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I8" s="11">
-        <x:v>3</x:v>
+      <x:c r="I8" s="11" t="s">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J8" s="12" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B9" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D9" s="11" t="s">
-        <x:v>33</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E9" s="11" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F9" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G9" s="11">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H9" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="I9" s="11">
-        <x:v>2</x:v>
+      <x:c r="I9" s="11" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J9" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B10" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D10" s="11" t="s">
-        <x:v>38</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E10" s="11" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F10" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G10" s="11">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H10" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H10" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="I10" s="11">
-        <x:v>2</x:v>
+      <x:c r="I10" s="11" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D11" s="11" t="s">
-        <x:v>43</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E11" s="11" t="s">
-        <x:v>39</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F11" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G11" s="11">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H11" s="11">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H11" s="11" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="I11" s="11">
-        <x:v>5</x:v>
+      <x:c r="I11" s="11" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J11" s="12" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B12" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D12" s="11" t="s">
-        <x:v>38</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E12" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F12" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G12" s="11">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H12" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H12" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="I12" s="11">
-        <x:v>3</x:v>
+      <x:c r="I12" s="11" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J12" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B13" s="11" t="s">
-        <x:v>47</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C13" s="11" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D13" s="11" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E13" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F13" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G13" s="11">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H13" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H13" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I13" s="11">
-        <x:v>2</x:v>
+      <x:c r="I13" s="11" t="s">
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B14" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D14" s="11" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E14" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F14" s="11" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G14" s="11">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H14" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H14" s="11" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="I14" s="11">
-        <x:v>3</x:v>
+      <x:c r="I14" s="11" t="s">
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C15" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D15" s="11" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E15" s="11" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F15" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G15" s="11">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H15" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H15" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="I15" s="11">
-        <x:v>2</x:v>
+      <x:c r="I15" s="11" t="s">
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B16" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D16" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E16" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H16" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10">
+      <x:c r="A17" s="10" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G16" s="11">
+      <x:c r="E17" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H17" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H16" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="I16" s="11">
+      <x:c r="I17" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:10">
+      <x:c r="A18" s="10" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H18" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:10">
-      <x:c r="A17" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B17" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D17" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="I18" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:10">
+      <x:c r="A19" s="10" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G17" s="14">
+      <x:c r="C19" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H19" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H17" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="I17" s="14">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>65</x:v>
+      <x:c r="I19" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:10">
+      <x:c r="A20" s="13" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H20" s="14">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I20" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
+        <x:v>92</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
